--- a/assets/constructions/examples/ctd_sha1.xlsx
+++ b/assets/constructions/examples/ctd_sha1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,31 +574,51 @@
           <t>cst</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BR-S-120100N002K044M7</t>
+          <t>DS-C16-M8-250</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BRICE</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BR-S-K</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BRICE_BR12</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -612,48 +632,32 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N2" t="n">
-        <v>12</v>
-      </c>
-      <c r="O2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="P2" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>100</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Carbide</t>
         </is>
       </c>
-      <c r="W2" t="b">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0.65</v>
+      </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
@@ -665,7 +669,7 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2018 / Каталог ввинчиваемых головок</t>
+          <t>2019 / DEREK</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -673,11 +677,17 @@
           <t>HA</t>
         </is>
       </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DS-C25-M12-200</t>
+          <t>DS-C25-M12-250</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -717,7 +727,7 @@
         <v>12.5</v>
       </c>
       <c r="L3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -735,7 +745,7 @@
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -756,31 +766,37 @@
           <t>HA</t>
         </is>
       </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DS-C20-M10-200</t>
+          <t>BR-S-120150N090</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>BRICE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>BR-S-N</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M10</t>
+          <t>BRICE_BR12</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -794,32 +810,44 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>10.5</v>
+        <v>11.7</v>
       </c>
       <c r="L4" t="n">
-        <v>200</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>12</v>
+      </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>150</v>
+      </c>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Carbide</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
-        <v>0.82</v>
-      </c>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
@@ -831,7 +859,7 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
+          <t>2018 / Каталог ввинчиваемых головок</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -839,11 +867,17 @@
           <t>HA</t>
         </is>
       </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BR-S-200080N040</t>
+          <t>BR-S-200150</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -853,7 +887,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BR-S-N</t>
+          <t>BR-S</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -883,20 +917,16 @@
         <v>19.5</v>
       </c>
       <c r="L5" t="n">
-        <v>80</v>
-      </c>
-      <c r="M5" t="n">
-        <v>19.5</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>20</v>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>40</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
@@ -934,80 +964,104 @@
           <t>HA</t>
         </is>
       </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STMC-C10.6L075M06</t>
+          <t>BR-S-160200N003K126M8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>BRICE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TMSD</t>
+          <t>BR-S-K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HA-10.6</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M6</t>
+          <t>BRICE_BR16</t>
         </is>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>10.6</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>11.7</v>
       </c>
       <c r="L6" t="n">
-        <v>75</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>200</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Steel</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
+          <t>Carbide</t>
+        </is>
+      </c>
+      <c r="W6" t="b">
+        <v>1</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2022 / Full MAIN VARDEX 2022-METRIC.pdf</t>
+          <t>2018 / Каталог ввинчиваемых головок</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1015,6 +1069,12 @@
           <t>HA</t>
         </is>
       </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
